--- a/ig/DM-37/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T08:55:07+00:00</t>
+    <t>2024-05-03T14:18:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T14:18:47+00:00</t>
+    <t>2024-05-03T14:27:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Association </t>
+    <t>Association  qui permet de deduire l'attribut XDS 'formatCode' à partir  de l'attribut 'component/nonXMLBody/text@mediaType' du CDA N1</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/DM-37/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T14:27:04+00:00</t>
+    <t>2024-05-03T14:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,9 +124,6 @@
   </si>
   <si>
     <t>urn:ihe:iti:xds-sd:text:2008</t>
-  </si>
-  <si>
-    <t>1.3.6.1.4.1.19376.1.2.20</t>
   </si>
   <si>
     <t>text/rtf</t>
@@ -400,7 +397,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -472,48 +469,35 @@
         <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>33</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="E8" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/DM-37/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T14:31:09+00:00</t>
+    <t>2024-05-03T15:46:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,22 +93,28 @@
     <t>Source</t>
   </si>
   <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV-MediaTypeCorpsCDANonStructure</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS</t>
+  </si>
+  <si>
     <t>Display</t>
   </si>
   <si>
     <t>Relationship</t>
   </si>
   <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV-MediaTypeCorpsCDANonStructure</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R222-MediaTypeCorpsCDANonStructure/FHIR/TRE-R222-MediaTypeCorpsCDANonStructure</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J10-XdsFormatCode-CISIS/FHIR/JDV-J10-XdsFormatCode-CISIS</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_A11-IheFormatCode/FHIR/TRE-A11-IheFormatCode</t>
   </si>
   <si>
     <t>application/pdf</t>
@@ -275,7 +281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -389,6 +395,22 @@
         <v>24</v>
       </c>
       <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -405,97 +427,97 @@
         <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>28</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2"/>
     </row>

--- a/ig/DM-37/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T15:46:37+00:00</t>
+    <t>2024-05-04T12:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T12:21:39+00:00</t>
+    <t>2024-05-04T13:53:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM-37/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T13:53:38+00:00</t>
+    <t>2024-05-04T15:01:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
